--- a/esyluban/examples/release/DataTables/role/等级信息表.xlsx
+++ b/esyluban/examples/release/DataTables/role/等级信息表.xlsx
@@ -9205,8 +9205,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="D1:M1"/>
-    <mergeCell ref="N1:X1"/>
+    <mergeCell ref="N2:X2"/>
+    <mergeCell ref="D2:M2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -9254,7 +9254,7 @@
           <t>*distinct_bonus_infos</t>
         </is>
       </c>
-      <c r="D2" s="33" t="n"/>
+      <c r="D2" s="32" t="n"/>
       <c r="E2" s="32" t="n"/>
       <c r="F2" s="32" t="n"/>
       <c r="G2" s="33" t="n"/>
@@ -9508,8 +9508,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="D3:G3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
